--- a/Results_experiment/exp_2/preds_1111122222222222.xlsx
+++ b/Results_experiment/exp_2/preds_1111122222222222.xlsx
@@ -1629,7 +1629,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D2">
-        <v>-2.667781114578247</v>
+        <v>-0.6335415840148926</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1643,7 +1643,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D3">
-        <v>1.765230894088745</v>
+        <v>0.153706818819046</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1657,7 +1657,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D4">
-        <v>-0.8628110885620117</v>
+        <v>-0.04450283944606781</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1671,7 +1671,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D5">
-        <v>-1.62159264087677</v>
+        <v>-3.587851285934448</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1685,7 +1685,7 @@
         <v>-19.29999923706055</v>
       </c>
       <c r="D6">
-        <v>-11.23405647277832</v>
+        <v>-12.5743350982666</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1699,7 +1699,7 @@
         <v>-14.10000038146973</v>
       </c>
       <c r="D7">
-        <v>-8.05499267578125</v>
+        <v>-4.888127326965332</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1713,7 +1713,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D8">
-        <v>-7.981233596801758</v>
+        <v>-9.083498954772949</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1727,7 +1727,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D9">
-        <v>1.639623522758484</v>
+        <v>0.9339635372161865</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1741,7 +1741,7 @@
         <v>-9.699999809265137</v>
       </c>
       <c r="D10">
-        <v>-9.050992012023926</v>
+        <v>-8.026961326599121</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1755,7 +1755,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D11">
-        <v>1.590901613235474</v>
+        <v>0.725749135017395</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1769,7 +1769,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D12">
-        <v>7.639254570007324</v>
+        <v>7.184799671173096</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1783,7 +1783,7 @@
         <v>-0.5</v>
       </c>
       <c r="D13">
-        <v>1.125980257987976</v>
+        <v>0.2831143140792847</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1797,7 +1797,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D14">
-        <v>0.4370088577270508</v>
+        <v>0.2742502093315125</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1811,7 +1811,7 @@
         <v>-9.800000190734863</v>
       </c>
       <c r="D15">
-        <v>-6.395481109619141</v>
+        <v>-7.26555347442627</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1825,7 +1825,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D16">
-        <v>-1.257018327713013</v>
+        <v>-0.562646746635437</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1839,7 +1839,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D17">
-        <v>3.695866346359253</v>
+        <v>3.089027166366577</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1853,7 +1853,7 @@
         <v>-10.5</v>
       </c>
       <c r="D18">
-        <v>-6.818629741668701</v>
+        <v>-5.072915554046631</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1867,7 +1867,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D19">
-        <v>-5.671947479248047</v>
+        <v>-4.626430034637451</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1881,7 +1881,7 @@
         <v>-23</v>
       </c>
       <c r="D20">
-        <v>-17.7175178527832</v>
+        <v>-19.79388618469238</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1895,7 +1895,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D21">
-        <v>-1.194491028785706</v>
+        <v>-2.972442865371704</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1909,7 +1909,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D22">
-        <v>-4.174808502197266</v>
+        <v>-7.285524845123291</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1923,7 +1923,7 @@
         <v>-22</v>
       </c>
       <c r="D23">
-        <v>-12.85325622558594</v>
+        <v>-13.67504501342773</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1937,7 +1937,7 @@
         <v>-9.5</v>
       </c>
       <c r="D24">
-        <v>-5.046450614929199</v>
+        <v>-5.93231725692749</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1951,7 +1951,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D25">
-        <v>-1.586872100830078</v>
+        <v>-0.8860007524490356</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1965,7 +1965,7 @@
         <v>-22.20000076293945</v>
       </c>
       <c r="D26">
-        <v>-15.80452728271484</v>
+        <v>-14.66876316070557</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1979,7 +1979,7 @@
         <v>6.5</v>
       </c>
       <c r="D27">
-        <v>1.177172303199768</v>
+        <v>1.20520031452179</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1993,7 +1993,7 @@
         <v>-20.29999923706055</v>
       </c>
       <c r="D28">
-        <v>-11.82631683349609</v>
+        <v>-12.14786815643311</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2007,7 +2007,7 @@
         <v>-15.19999980926514</v>
       </c>
       <c r="D29">
-        <v>-9.495976448059082</v>
+        <v>-14.25050067901611</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2021,7 +2021,7 @@
         <v>-2</v>
       </c>
       <c r="D30">
-        <v>-6.947994232177734</v>
+        <v>-3.338718891143799</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2035,7 +2035,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D31">
-        <v>-6.871726989746094</v>
+        <v>-8.103753089904785</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2049,7 +2049,7 @@
         <v>-11.30000019073486</v>
       </c>
       <c r="D32">
-        <v>-11.13449668884277</v>
+        <v>-10.4898099899292</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2063,7 +2063,7 @@
         <v>26.39999961853027</v>
       </c>
       <c r="D33">
-        <v>18.13293075561523</v>
+        <v>15.88401889801025</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2077,7 +2077,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D34">
-        <v>7.350486278533936</v>
+        <v>5.924331188201904</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2091,7 +2091,7 @@
         <v>4.5</v>
       </c>
       <c r="D35">
-        <v>2.143076658248901</v>
+        <v>1.409594893455505</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2105,7 +2105,7 @@
         <v>5</v>
       </c>
       <c r="D36">
-        <v>3.219638586044312</v>
+        <v>2.024449348449707</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2119,7 +2119,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D37">
-        <v>2.432621479034424</v>
+        <v>2.471985578536987</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2133,7 +2133,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D38">
-        <v>-4.443685531616211</v>
+        <v>-3.290786504745483</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2147,7 +2147,7 @@
         <v>26.5</v>
       </c>
       <c r="D39">
-        <v>18.42256164550781</v>
+        <v>16.67282485961914</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2161,7 +2161,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D40">
-        <v>-2.066144466400146</v>
+        <v>-0.5617544054985046</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2175,7 +2175,7 @@
         <v>7</v>
       </c>
       <c r="D41">
-        <v>0.7717317342758179</v>
+        <v>1.904770612716675</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2189,7 +2189,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D42">
-        <v>1.975723385810852</v>
+        <v>0.3207176923751831</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2203,7 +2203,7 @@
         <v>-16.70000076293945</v>
       </c>
       <c r="D43">
-        <v>-13.90604019165039</v>
+        <v>-14.34750747680664</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2217,7 +2217,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D44">
-        <v>-6.157471179962158</v>
+        <v>-5.603176116943359</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2231,7 +2231,7 @@
         <v>-0.5</v>
       </c>
       <c r="D45">
-        <v>-0.1603775769472122</v>
+        <v>0.5332405567169189</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2245,7 +2245,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D46">
-        <v>-0.6210387945175171</v>
+        <v>0.03494780510663986</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2259,7 +2259,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D47">
-        <v>2.202086210250854</v>
+        <v>2.221960067749023</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2273,7 +2273,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D48">
-        <v>-2.021982908248901</v>
+        <v>-1.600489616394043</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2287,7 +2287,7 @@
         <v>-9</v>
       </c>
       <c r="D49">
-        <v>-4.310175895690918</v>
+        <v>-4.996605396270752</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2301,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="D50">
-        <v>0.4078372120857239</v>
+        <v>0.8954958915710449</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2315,7 +2315,7 @@
         <v>-7</v>
       </c>
       <c r="D51">
-        <v>-1.07408332824707</v>
+        <v>-2.394344091415405</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2329,7 +2329,7 @@
         <v>-4</v>
       </c>
       <c r="D52">
-        <v>-3.297853231430054</v>
+        <v>-2.512177228927612</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2343,7 +2343,7 @@
         <v>4.5</v>
       </c>
       <c r="D53">
-        <v>2.039375782012939</v>
+        <v>1.37063992023468</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2357,7 +2357,7 @@
         <v>0.5</v>
       </c>
       <c r="D54">
-        <v>1.234001994132996</v>
+        <v>2.417357206344604</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2371,7 +2371,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D55">
-        <v>6.221504211425781</v>
+        <v>4.627074718475342</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2385,7 +2385,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D56">
-        <v>7.766273975372314</v>
+        <v>5.433326244354248</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2399,7 +2399,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D57">
-        <v>-21.54391479492188</v>
+        <v>-20.68656539916992</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2413,7 +2413,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D58">
-        <v>-3.483494520187378</v>
+        <v>-6.413563251495361</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2427,7 +2427,7 @@
         <v>-24.20000076293945</v>
       </c>
       <c r="D59">
-        <v>-12.90596199035645</v>
+        <v>-16.08947944641113</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2441,7 +2441,7 @@
         <v>-24.39999961853027</v>
       </c>
       <c r="D60">
-        <v>-19.2032585144043</v>
+        <v>-16.95731353759766</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2455,7 +2455,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D61">
-        <v>4.110925674438477</v>
+        <v>2.717543125152588</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2469,7 +2469,7 @@
         <v>0.5</v>
       </c>
       <c r="D62">
-        <v>-0.3865624666213989</v>
+        <v>-0.3635088801383972</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2483,7 +2483,7 @@
         <v>-9.100000381469727</v>
       </c>
       <c r="D63">
-        <v>-9.479681968688965</v>
+        <v>-9.177006721496582</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2497,7 +2497,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D64">
-        <v>-3.261236667633057</v>
+        <v>-0.1843603700399399</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2511,7 +2511,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D65">
-        <v>2.138633489608765</v>
+        <v>3.105756044387817</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2525,7 +2525,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D66">
-        <v>-4.449724197387695</v>
+        <v>-3.35350775718689</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2539,7 +2539,7 @@
         <v>-1</v>
       </c>
       <c r="D67">
-        <v>0.945928692817688</v>
+        <v>-0.5745117664337158</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2553,7 +2553,7 @@
         <v>-7.599999904632568</v>
       </c>
       <c r="D68">
-        <v>-5.51312255859375</v>
+        <v>-5.687270641326904</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2567,7 +2567,7 @@
         <v>-4.5</v>
       </c>
       <c r="D69">
-        <v>-2.975372076034546</v>
+        <v>-2.133273839950562</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2581,7 +2581,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D70">
-        <v>-0.7245139479637146</v>
+        <v>-1.544485569000244</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2595,7 +2595,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D71">
-        <v>-2.307277917861938</v>
+        <v>0.929158091545105</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2609,7 +2609,7 @@
         <v>-15</v>
       </c>
       <c r="D72">
-        <v>-10.05364227294922</v>
+        <v>-8.543840408325195</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2623,7 +2623,7 @@
         <v>8.5</v>
       </c>
       <c r="D73">
-        <v>12.7360258102417</v>
+        <v>10.18427753448486</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2637,7 +2637,7 @@
         <v>-8.199999809265137</v>
       </c>
       <c r="D74">
-        <v>-1.156098127365112</v>
+        <v>-0.06019073724746704</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2651,7 +2651,7 @@
         <v>16.60000038146973</v>
       </c>
       <c r="D75">
-        <v>9.441593170166016</v>
+        <v>8.726584434509277</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2665,7 +2665,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D76">
-        <v>-2.55840015411377</v>
+        <v>-1.540987968444824</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2679,7 +2679,7 @@
         <v>-13.19999980926514</v>
       </c>
       <c r="D77">
-        <v>-3.698437929153442</v>
+        <v>-3.732016324996948</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2693,7 +2693,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D78">
-        <v>-1.373819828033447</v>
+        <v>-4.002011299133301</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2707,7 +2707,7 @@
         <v>-1</v>
       </c>
       <c r="D79">
-        <v>-2.001745939254761</v>
+        <v>-0.9385285377502441</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2721,7 +2721,7 @@
         <v>-8.5</v>
       </c>
       <c r="D80">
-        <v>0.7732691764831543</v>
+        <v>-0.6491109728813171</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2735,7 +2735,7 @@
         <v>-8.699999809265137</v>
       </c>
       <c r="D81">
-        <v>-3.238329172134399</v>
+        <v>-1.437439680099487</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2749,7 +2749,7 @@
         <v>4</v>
       </c>
       <c r="D82">
-        <v>4.493720531463623</v>
+        <v>4.834449768066406</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2763,7 +2763,7 @@
         <v>-34.79999923706055</v>
       </c>
       <c r="D83">
-        <v>-14.98592090606689</v>
+        <v>-12.50654983520508</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2777,7 +2777,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D84">
-        <v>-2.511094808578491</v>
+        <v>-2.656231641769409</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2791,7 +2791,7 @@
         <v>-29</v>
       </c>
       <c r="D85">
-        <v>-7.995792388916016</v>
+        <v>-4.843903064727783</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2805,7 +2805,7 @@
         <v>-15.10000038146973</v>
       </c>
       <c r="D86">
-        <v>-7.089372634887695</v>
+        <v>-7.967257976531982</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2819,7 +2819,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D87">
-        <v>-0.5246778130531311</v>
+        <v>-1.786518335342407</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2833,7 +2833,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D88">
-        <v>8.040057182312012</v>
+        <v>8.01280403137207</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2847,7 +2847,7 @@
         <v>-12.30000019073486</v>
       </c>
       <c r="D89">
-        <v>-12.4734582901001</v>
+        <v>-11.6738748550415</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2861,7 +2861,7 @@
         <v>-9</v>
       </c>
       <c r="D90">
-        <v>-4.368412017822266</v>
+        <v>-4.584820747375488</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2875,7 +2875,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D91">
-        <v>4.482457637786865</v>
+        <v>6.147826671600342</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2889,7 +2889,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D92">
-        <v>2.229456663131714</v>
+        <v>3.140211820602417</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2903,7 +2903,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D93">
-        <v>5.339972972869873</v>
+        <v>6.077781200408936</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2917,7 +2917,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D94">
-        <v>-2.004057645797729</v>
+        <v>0.4030231237411499</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2931,7 +2931,7 @@
         <v>2</v>
       </c>
       <c r="D95">
-        <v>0.4818983674049377</v>
+        <v>-0.5214701890945435</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2945,7 +2945,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D96">
-        <v>-1.094957113265991</v>
+        <v>-0.4706592559814453</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2959,7 +2959,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D97">
-        <v>0.8582892417907715</v>
+        <v>0.3243905901908875</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2973,7 +2973,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D98">
-        <v>2.401721239089966</v>
+        <v>2.43523645401001</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2987,7 +2987,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D99">
-        <v>1.007384657859802</v>
+        <v>-0.1088418811559677</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3001,7 +3001,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D100">
-        <v>1.86250376701355</v>
+        <v>1.311829686164856</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3015,7 +3015,7 @@
         <v>4</v>
       </c>
       <c r="D101">
-        <v>-2.641902446746826</v>
+        <v>-2.818600416183472</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3029,7 +3029,7 @@
         <v>5.5</v>
       </c>
       <c r="D102">
-        <v>2.371297121047974</v>
+        <v>2.783681154251099</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3043,7 +3043,7 @@
         <v>19.5</v>
       </c>
       <c r="D103">
-        <v>8.281789779663086</v>
+        <v>6.070789813995361</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3057,7 +3057,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D104">
-        <v>3.552483320236206</v>
+        <v>3.534931898117065</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3071,7 +3071,7 @@
         <v>-21.5</v>
       </c>
       <c r="D105">
-        <v>-15.02721118927002</v>
+        <v>-11.09380722045898</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3085,7 +3085,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D106">
-        <v>-2.431001424789429</v>
+        <v>-2.62000846862793</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3099,7 +3099,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D107">
-        <v>4.853196144104004</v>
+        <v>5.455757617950439</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3113,7 +3113,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D108">
-        <v>-2.744915723800659</v>
+        <v>-3.055013179779053</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3127,7 +3127,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D109">
-        <v>-1.206015825271606</v>
+        <v>0.4873730540275574</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3141,7 +3141,7 @@
         <v>10.5</v>
       </c>
       <c r="D110">
-        <v>6.440582275390625</v>
+        <v>5.298026561737061</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3155,7 +3155,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D111">
-        <v>1.415428400039673</v>
+        <v>2.161139726638794</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3169,7 +3169,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D112">
-        <v>-1.858510971069336</v>
+        <v>-6.650361061096191</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3183,7 +3183,7 @@
         <v>-18.5</v>
       </c>
       <c r="D113">
-        <v>-8.640985488891602</v>
+        <v>-6.0735764503479</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3197,7 +3197,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D114">
-        <v>-21.64114570617676</v>
+        <v>-21.43459510803223</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3211,7 +3211,7 @@
         <v>-32.09999847412109</v>
       </c>
       <c r="D115">
-        <v>-12.75914192199707</v>
+        <v>-15.83513355255127</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3225,7 +3225,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D116">
-        <v>-2.075022459030151</v>
+        <v>-2.40049409866333</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3239,7 +3239,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D117">
-        <v>7.256978988647461</v>
+        <v>7.200466156005859</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3253,7 +3253,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D118">
-        <v>1.005719900131226</v>
+        <v>0.06007207185029984</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3267,7 +3267,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D119">
-        <v>0.3195889294147491</v>
+        <v>-0.7489493489265442</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3281,7 +3281,7 @@
         <v>43.59999847412109</v>
       </c>
       <c r="D120">
-        <v>22.8960075378418</v>
+        <v>23.35730171203613</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3295,7 +3295,7 @@
         <v>-21.29999923706055</v>
       </c>
       <c r="D121">
-        <v>-27.08721733093262</v>
+        <v>-24.01107978820801</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3309,7 +3309,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D122">
-        <v>1.800533056259155</v>
+        <v>0.6119834184646606</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3323,7 +3323,7 @@
         <v>-9.300000190734863</v>
       </c>
       <c r="D123">
-        <v>-4.102499961853027</v>
+        <v>-3.604494571685791</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3337,7 +3337,7 @@
         <v>1</v>
       </c>
       <c r="D124">
-        <v>3.154547452926636</v>
+        <v>2.856733798980713</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3351,7 +3351,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D125">
-        <v>-0.9401792287826538</v>
+        <v>0.6426802277565002</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3365,7 +3365,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D126">
-        <v>9.342758178710938</v>
+        <v>8.697245597839355</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3379,7 +3379,7 @@
         <v>-17.10000038146973</v>
       </c>
       <c r="D127">
-        <v>-6.786046028137207</v>
+        <v>-6.550083637237549</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3393,7 +3393,7 @@
         <v>-8</v>
       </c>
       <c r="D128">
-        <v>-5.80402660369873</v>
+        <v>-4.891462326049805</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3407,7 +3407,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D129">
-        <v>-1.693976879119873</v>
+        <v>-1.992122888565063</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3421,7 +3421,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D130">
-        <v>-3.850842714309692</v>
+        <v>-4.665072917938232</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3435,7 +3435,7 @@
         <v>-2</v>
       </c>
       <c r="D131">
-        <v>-3.213242530822754</v>
+        <v>-4.588646411895752</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3449,7 +3449,7 @@
         <v>-1</v>
       </c>
       <c r="D132">
-        <v>-0.104806587100029</v>
+        <v>-0.813599705696106</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3463,7 +3463,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D133">
-        <v>-1.160336971282959</v>
+        <v>0.2058211266994476</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3477,7 +3477,7 @@
         <v>-10.39999961853027</v>
       </c>
       <c r="D134">
-        <v>-1.520851254463196</v>
+        <v>-0.8041579723358154</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3491,7 +3491,7 @@
         <v>-7.099999904632568</v>
       </c>
       <c r="D135">
-        <v>-0.9067665338516235</v>
+        <v>0.1771591901779175</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3505,7 +3505,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D136">
-        <v>1.267906904220581</v>
+        <v>-0.5155363082885742</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3519,7 +3519,7 @@
         <v>-12.30000019073486</v>
       </c>
       <c r="D137">
-        <v>-11.34517478942871</v>
+        <v>-9.43329906463623</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3533,7 +3533,7 @@
         <v>-3.5</v>
       </c>
       <c r="D138">
-        <v>1.196351289749146</v>
+        <v>0.3557049036026001</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3547,7 +3547,7 @@
         <v>8</v>
       </c>
       <c r="D139">
-        <v>7.283050060272217</v>
+        <v>7.531383514404297</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3561,7 +3561,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D140">
-        <v>0.7938959002494812</v>
+        <v>-0.7264147400856018</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3575,7 +3575,7 @@
         <v>-28.70000076293945</v>
       </c>
       <c r="D141">
-        <v>-16.16622543334961</v>
+        <v>-21.56118774414062</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3589,7 +3589,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D142">
-        <v>-6.833822727203369</v>
+        <v>-2.975660562515259</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3603,7 +3603,7 @@
         <v>10.69999980926514</v>
       </c>
       <c r="D143">
-        <v>4.335024833679199</v>
+        <v>3.466234922409058</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3617,7 +3617,7 @@
         <v>-7.699999809265137</v>
       </c>
       <c r="D144">
-        <v>-0.1856278926134109</v>
+        <v>-1.165112614631653</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3631,7 +3631,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D145">
-        <v>-6.648027896881104</v>
+        <v>-6.583005905151367</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3645,7 +3645,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D146">
-        <v>4.117560863494873</v>
+        <v>3.073536157608032</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3659,7 +3659,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D147">
-        <v>2.406401395797729</v>
+        <v>3.685413599014282</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3673,7 +3673,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D148">
-        <v>0.7330402135848999</v>
+        <v>0.08657907694578171</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3687,7 +3687,7 @@
         <v>13.19999980926514</v>
       </c>
       <c r="D149">
-        <v>7.036167144775391</v>
+        <v>6.120695114135742</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3701,7 +3701,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D150">
-        <v>1.201221823692322</v>
+        <v>1.563233852386475</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3715,7 +3715,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D151">
-        <v>-4.960321426391602</v>
+        <v>-4.780889511108398</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3729,7 +3729,7 @@
         <v>-10.80000019073486</v>
       </c>
       <c r="D152">
-        <v>-9.371683120727539</v>
+        <v>-6.764301300048828</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3743,7 +3743,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D153">
-        <v>-10.34934043884277</v>
+        <v>-6.427685260772705</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3757,7 +3757,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D154">
-        <v>-2.27350640296936</v>
+        <v>-4.789829730987549</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3771,7 +3771,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D155">
-        <v>1.415601849555969</v>
+        <v>1.129214286804199</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>0.5739583969116211</v>
+        <v>-0.3161182999610901</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3799,7 +3799,7 @@
         <v>26.29999923706055</v>
       </c>
       <c r="D157">
-        <v>17.50226211547852</v>
+        <v>14.94225406646729</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3813,7 +3813,7 @@
         <v>-16</v>
       </c>
       <c r="D158">
-        <v>-8.096173286437988</v>
+        <v>-7.704785346984863</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3827,7 +3827,7 @@
         <v>0.5</v>
       </c>
       <c r="D159">
-        <v>-3.923797845840454</v>
+        <v>-1.144068479537964</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3841,7 +3841,7 @@
         <v>27.79999923706055</v>
       </c>
       <c r="D160">
-        <v>12.81641483306885</v>
+        <v>13.46418857574463</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3855,7 +3855,7 @@
         <v>41.79999923706055</v>
       </c>
       <c r="D161">
-        <v>16.81950759887695</v>
+        <v>15.31271266937256</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3869,7 +3869,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D162">
-        <v>2.343998670578003</v>
+        <v>1.593595027923584</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3883,7 +3883,7 @@
         <v>0.5</v>
       </c>
       <c r="D163">
-        <v>2.082333326339722</v>
+        <v>1.640399217605591</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3897,7 +3897,7 @@
         <v>-19.79999923706055</v>
       </c>
       <c r="D164">
-        <v>-7.469927787780762</v>
+        <v>-13.03166484832764</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3911,7 +3911,7 @@
         <v>-8.800000190734863</v>
       </c>
       <c r="D165">
-        <v>-1.201269268989563</v>
+        <v>-3.356324911117554</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3925,7 +3925,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D166">
-        <v>-1.047735810279846</v>
+        <v>-2.929819345474243</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3939,7 +3939,7 @@
         <v>-5</v>
       </c>
       <c r="D167">
-        <v>-1.69976282119751</v>
+        <v>-2.248650312423706</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3953,7 +3953,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D168">
-        <v>-3.900665998458862</v>
+        <v>-4.369843006134033</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3967,7 +3967,7 @@
         <v>-10.30000019073486</v>
       </c>
       <c r="D169">
-        <v>-11.14766120910645</v>
+        <v>-11.19068241119385</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3981,7 +3981,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D170">
-        <v>3.254480600357056</v>
+        <v>3.616977453231812</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3995,7 +3995,7 @@
         <v>-11.80000019073486</v>
       </c>
       <c r="D171">
-        <v>-7.409112930297852</v>
+        <v>-8.751960754394531</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4009,7 +4009,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D172">
-        <v>2.688159465789795</v>
+        <v>3.968823194503784</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4023,7 +4023,7 @@
         <v>-18.20000076293945</v>
       </c>
       <c r="D173">
-        <v>-12.31991386413574</v>
+        <v>-12.31060123443604</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4037,7 +4037,7 @@
         <v>-3</v>
       </c>
       <c r="D174">
-        <v>1.333829164505005</v>
+        <v>2.819060087203979</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4051,7 +4051,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D175">
-        <v>1.043044090270996</v>
+        <v>0.6983685493469238</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4065,7 +4065,7 @@
         <v>-14</v>
       </c>
       <c r="D176">
-        <v>-9.165307998657227</v>
+        <v>-4.203354358673096</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4079,7 +4079,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D177">
-        <v>-0.7560280561447144</v>
+        <v>-1.069676876068115</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4093,7 +4093,7 @@
         <v>12.10000038146973</v>
       </c>
       <c r="D178">
-        <v>9.333589553833008</v>
+        <v>8.525825500488281</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4107,7 +4107,7 @@
         <v>-13.10000038146973</v>
       </c>
       <c r="D179">
-        <v>-7.23995304107666</v>
+        <v>-5.532209396362305</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4121,7 +4121,7 @@
         <v>-18.79999923706055</v>
       </c>
       <c r="D180">
-        <v>-13.04637813568115</v>
+        <v>-11.51212024688721</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4135,7 +4135,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D181">
-        <v>2.359496831893921</v>
+        <v>1.266715526580811</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4149,7 +4149,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D182">
-        <v>1.232863306999207</v>
+        <v>0.4252820611000061</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4163,7 +4163,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D183">
-        <v>1.701388359069824</v>
+        <v>5.271214962005615</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4177,7 +4177,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D184">
-        <v>5.646973133087158</v>
+        <v>5.280332088470459</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4191,7 +4191,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D185">
-        <v>2.658385038375854</v>
+        <v>1.413749575614929</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4205,7 +4205,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D186">
-        <v>1.396265268325806</v>
+        <v>1.145201683044434</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4219,7 +4219,7 @@
         <v>-13.80000019073486</v>
       </c>
       <c r="D187">
-        <v>-10.73624801635742</v>
+        <v>-14.18473434448242</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4233,7 +4233,7 @@
         <v>-6.599999904632568</v>
       </c>
       <c r="D188">
-        <v>1.267319202423096</v>
+        <v>0.06855962425470352</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4247,7 +4247,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D189">
-        <v>1.854009389877319</v>
+        <v>2.304003953933716</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4261,7 +4261,7 @@
         <v>5.5</v>
       </c>
       <c r="D190">
-        <v>-2.404182195663452</v>
+        <v>0.2949221134185791</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4275,7 +4275,7 @@
         <v>-10.10000038146973</v>
       </c>
       <c r="D191">
-        <v>-11.35788345336914</v>
+        <v>-11.08768272399902</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4289,7 +4289,7 @@
         <v>2</v>
       </c>
       <c r="D192">
-        <v>2.042520761489868</v>
+        <v>0.8310332298278809</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4303,7 +4303,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D193">
-        <v>3.446011543273926</v>
+        <v>2.860597372055054</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4317,7 +4317,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D194">
-        <v>-3.549990177154541</v>
+        <v>-3.03371524810791</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4331,7 +4331,7 @@
         <v>0.5</v>
       </c>
       <c r="D195">
-        <v>1.719187498092651</v>
+        <v>0.7282436490058899</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4345,7 +4345,7 @@
         <v>32.59999847412109</v>
       </c>
       <c r="D196">
-        <v>22.55514144897461</v>
+        <v>22.92607307434082</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4359,7 +4359,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D197">
-        <v>8.576190948486328</v>
+        <v>10.95540332794189</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4373,7 +4373,7 @@
         <v>-22.89999961853027</v>
       </c>
       <c r="D198">
-        <v>-5.209702014923096</v>
+        <v>-2.834152460098267</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4387,7 +4387,7 @@
         <v>-20.89999961853027</v>
       </c>
       <c r="D199">
-        <v>-11.81603145599365</v>
+        <v>-12.85326194763184</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4401,7 +4401,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D200">
-        <v>1.571273684501648</v>
+        <v>-1.090521097183228</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4415,7 +4415,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D201">
-        <v>-2.426274538040161</v>
+        <v>-2.781534433364868</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4429,7 +4429,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D202">
-        <v>1.841603398323059</v>
+        <v>2.325220823287964</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4443,7 +4443,7 @@
         <v>-4.5</v>
       </c>
       <c r="D203">
-        <v>-3.811594486236572</v>
+        <v>-4.300266742706299</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4457,7 +4457,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D204">
-        <v>11.25615119934082</v>
+        <v>8.698953628540039</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4471,7 +4471,7 @@
         <v>-2.5</v>
       </c>
       <c r="D205">
-        <v>-0.3332082033157349</v>
+        <v>0.1697895526885986</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4485,7 +4485,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D206">
-        <v>3.318121671676636</v>
+        <v>3.847028493881226</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4499,7 +4499,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D207">
-        <v>5.129837036132812</v>
+        <v>5.864556789398193</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4513,7 +4513,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D208">
-        <v>-5.601724147796631</v>
+        <v>1.220771670341492</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4527,7 +4527,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D209">
-        <v>-1.71873950958252</v>
+        <v>-1.420889616012573</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4541,7 +4541,7 @@
         <v>-4</v>
       </c>
       <c r="D210">
-        <v>7.774877071380615</v>
+        <v>-0.1814550012350082</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4555,7 +4555,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D211">
-        <v>-1.350558757781982</v>
+        <v>3.220900774002075</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4569,7 +4569,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D212">
-        <v>-2.891821146011353</v>
+        <v>-3.915713548660278</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4583,7 +4583,7 @@
         <v>-6</v>
       </c>
       <c r="D213">
-        <v>2.667624235153198</v>
+        <v>1.750216126441956</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4597,7 +4597,7 @@
         <v>-15.30000019073486</v>
       </c>
       <c r="D214">
-        <v>0.9014239907264709</v>
+        <v>-1.614697694778442</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4611,7 +4611,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D215">
-        <v>3.178487062454224</v>
+        <v>3.872407674789429</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4625,7 +4625,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D216">
-        <v>-0.7874302268028259</v>
+        <v>-0.453615665435791</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4639,7 +4639,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D217">
-        <v>-3.762852430343628</v>
+        <v>-2.421245098114014</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4653,7 +4653,7 @@
         <v>5.5</v>
       </c>
       <c r="D218">
-        <v>5.36534309387207</v>
+        <v>4.622106075286865</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4667,7 +4667,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D219">
-        <v>-0.8873077630996704</v>
+        <v>-0.9916627407073975</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4681,7 +4681,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D220">
-        <v>1.748138904571533</v>
+        <v>1.111852765083313</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4695,7 +4695,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D221">
-        <v>0.6105480790138245</v>
+        <v>1.245097279548645</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4709,7 +4709,7 @@
         <v>-10.80000019073486</v>
       </c>
       <c r="D222">
-        <v>-11.20018482208252</v>
+        <v>-8.016704559326172</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4723,7 +4723,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D223">
-        <v>6.175601005554199</v>
+        <v>4.886575222015381</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4737,7 +4737,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D224">
-        <v>-0.8962893486022949</v>
+        <v>0.1538106203079224</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4751,7 +4751,7 @@
         <v>-25.79999923706055</v>
       </c>
       <c r="D225">
-        <v>-13.6750545501709</v>
+        <v>-14.13693618774414</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4765,7 +4765,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D226">
-        <v>5.550206184387207</v>
+        <v>5.324123859405518</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4779,7 +4779,7 @@
         <v>12</v>
       </c>
       <c r="D227">
-        <v>-4.284860134124756</v>
+        <v>-3.981040239334106</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4793,7 +4793,7 @@
         <v>-26.60000038146973</v>
       </c>
       <c r="D228">
-        <v>-11.31595230102539</v>
+        <v>-15.45040607452393</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4807,7 +4807,7 @@
         <v>-17.70000076293945</v>
       </c>
       <c r="D229">
-        <v>-11.52615070343018</v>
+        <v>-12.05600547790527</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4821,7 +4821,7 @@
         <v>-9.600000381469727</v>
       </c>
       <c r="D230">
-        <v>-8.130226135253906</v>
+        <v>-3.530677080154419</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4835,7 +4835,7 @@
         <v>-18.5</v>
       </c>
       <c r="D231">
-        <v>-14.42036056518555</v>
+        <v>-14.60510730743408</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4849,7 +4849,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D232">
-        <v>0.2415544092655182</v>
+        <v>-1.109394788742065</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4863,7 +4863,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D233">
-        <v>1.961792707443237</v>
+        <v>0.4773577451705933</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4877,7 +4877,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D234">
-        <v>-3.241283893585205</v>
+        <v>-1.910932064056396</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4891,7 +4891,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D235">
-        <v>1.774603724479675</v>
+        <v>1.109382390975952</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4905,7 +4905,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D236">
-        <v>-2.506622314453125</v>
+        <v>-3.29632830619812</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4919,7 +4919,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D237">
-        <v>6.137960910797119</v>
+        <v>4.80470609664917</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4933,7 +4933,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D238">
-        <v>-0.5516117811203003</v>
+        <v>0.2678411602973938</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4947,7 +4947,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D239">
-        <v>4.93533182144165</v>
+        <v>5.228515148162842</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4961,7 +4961,7 @@
         <v>5.5</v>
       </c>
       <c r="D240">
-        <v>5.323586940765381</v>
+        <v>4.657296180725098</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4975,7 +4975,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D241">
-        <v>3.378202676773071</v>
+        <v>2.136804103851318</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4989,7 +4989,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D242">
-        <v>-2.824472427368164</v>
+        <v>-1.80302894115448</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5003,7 +5003,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D243">
-        <v>2.198857069015503</v>
+        <v>1.125906825065613</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5017,7 +5017,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D244">
-        <v>2.657696008682251</v>
+        <v>2.618070840835571</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5031,7 +5031,7 @@
         <v>-8.100000381469727</v>
       </c>
       <c r="D245">
-        <v>-1.909107208251953</v>
+        <v>-3.284604787826538</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5045,7 +5045,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D246">
-        <v>3.116199731826782</v>
+        <v>3.509692668914795</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5059,7 +5059,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D247">
-        <v>3.427814483642578</v>
+        <v>2.358989715576172</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5073,7 +5073,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D248">
-        <v>-5.505250453948975</v>
+        <v>-6.499144077301025</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5087,7 +5087,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D249">
-        <v>-2.029845476150513</v>
+        <v>-3.356704950332642</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5101,7 +5101,7 @@
         <v>-8.699999809265137</v>
       </c>
       <c r="D250">
-        <v>-4.994645118713379</v>
+        <v>-5.114244937896729</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5115,7 +5115,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D251">
-        <v>4.354856014251709</v>
+        <v>3.735411405563354</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5129,7 +5129,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D252">
-        <v>1.953215003013611</v>
+        <v>0.9945379495620728</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5143,7 +5143,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D253">
-        <v>-4.079935073852539</v>
+        <v>-4.011421680450439</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5157,7 +5157,7 @@
         <v>12.10000038146973</v>
       </c>
       <c r="D254">
-        <v>8.201148986816406</v>
+        <v>6.859994411468506</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5171,7 +5171,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D255">
-        <v>4.162729740142822</v>
+        <v>3.712037324905396</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5185,7 +5185,7 @@
         <v>-7.5</v>
       </c>
       <c r="D256">
-        <v>-5.393249988555908</v>
+        <v>-5.286054134368896</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -5199,7 +5199,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D257">
-        <v>1.237831354141235</v>
+        <v>-1.163488388061523</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -5213,7 +5213,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D258">
-        <v>1.705081462860107</v>
+        <v>2.262113809585571</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -5227,7 +5227,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D259">
-        <v>-4.213272571563721</v>
+        <v>-0.8674280047416687</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -5241,7 +5241,7 @@
         <v>-7</v>
       </c>
       <c r="D260">
-        <v>-5.909189701080322</v>
+        <v>-5.352668285369873</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -5255,7 +5255,7 @@
         <v>-13.69999980926514</v>
       </c>
       <c r="D261">
-        <v>-11.65371704101562</v>
+        <v>-10.90542697906494</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -5269,7 +5269,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D262">
-        <v>3.502383232116699</v>
+        <v>2.344759702682495</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -5283,7 +5283,7 @@
         <v>3.5</v>
       </c>
       <c r="D263">
-        <v>2.447295427322388</v>
+        <v>1.678079009056091</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -5297,7 +5297,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D264">
-        <v>1.802297353744507</v>
+        <v>-0.2230361551046371</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -5311,7 +5311,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D265">
-        <v>-10.02629852294922</v>
+        <v>-10.55052471160889</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -5325,7 +5325,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D266">
-        <v>1.108438372612</v>
+        <v>0.4551007747650146</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -5339,7 +5339,7 @@
         <v>-14</v>
       </c>
       <c r="D267">
-        <v>-6.72450065612793</v>
+        <v>-5.749877452850342</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -5353,7 +5353,7 @@
         <v>3.5</v>
       </c>
       <c r="D268">
-        <v>-3.097011804580688</v>
+        <v>-2.151192426681519</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -5367,7 +5367,7 @@
         <v>-11.30000019073486</v>
       </c>
       <c r="D269">
-        <v>-3.842224836349487</v>
+        <v>-7.397646903991699</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -5381,7 +5381,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D270">
-        <v>1.06503689289093</v>
+        <v>0.7416335344314575</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5395,7 +5395,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D271">
-        <v>0.9834046959877014</v>
+        <v>0.7978043556213379</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5409,7 +5409,7 @@
         <v>-22.29999923706055</v>
       </c>
       <c r="D272">
-        <v>-11.9446964263916</v>
+        <v>-13.10241508483887</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5423,7 +5423,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D273">
-        <v>4.943009376525879</v>
+        <v>4.274589061737061</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5437,7 +5437,7 @@
         <v>-13.19999980926514</v>
       </c>
       <c r="D274">
-        <v>-12.08053207397461</v>
+        <v>-11.83491325378418</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5451,7 +5451,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D275">
-        <v>1.722182035446167</v>
+        <v>1.12292218208313</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5465,7 +5465,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D276">
-        <v>-3.842198133468628</v>
+        <v>-2.332165002822876</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5479,7 +5479,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D277">
-        <v>3.474692583084106</v>
+        <v>2.64021372795105</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5493,7 +5493,7 @@
         <v>5.5</v>
       </c>
       <c r="D278">
-        <v>0.4565284848213196</v>
+        <v>1.568354368209839</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5507,7 +5507,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D279">
-        <v>2.087870836257935</v>
+        <v>2.353101968765259</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5521,7 +5521,7 @@
         <v>-9.199999809265137</v>
       </c>
       <c r="D280">
-        <v>-13.2363395690918</v>
+        <v>-8.496941566467285</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5535,7 +5535,7 @@
         <v>-19</v>
       </c>
       <c r="D281">
-        <v>-12.18899726867676</v>
+        <v>-15.73582744598389</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5549,7 +5549,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D282">
-        <v>2.651504755020142</v>
+        <v>1.292943954467773</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5563,7 +5563,7 @@
         <v>-2.5</v>
       </c>
       <c r="D283">
-        <v>-1.633307933807373</v>
+        <v>-2.577268362045288</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5577,7 +5577,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D284">
-        <v>2.613705396652222</v>
+        <v>1.886854410171509</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5591,7 +5591,7 @@
         <v>-7</v>
       </c>
       <c r="D285">
-        <v>-8.781360626220703</v>
+        <v>-2.848430156707764</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5605,7 +5605,7 @@
         <v>-16.79999923706055</v>
       </c>
       <c r="D286">
-        <v>-12.50330829620361</v>
+        <v>-11.86616992950439</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5619,7 +5619,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D287">
-        <v>2.373594522476196</v>
+        <v>1.561270236968994</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5633,7 +5633,7 @@
         <v>10.19999980926514</v>
       </c>
       <c r="D288">
-        <v>-0.7518506050109863</v>
+        <v>1.792964100837708</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5647,7 +5647,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D289">
-        <v>8.751611709594727</v>
+        <v>6.823290824890137</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5661,7 +5661,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D290">
-        <v>2.467894315719604</v>
+        <v>0.4979679584503174</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5675,7 +5675,7 @@
         <v>-27.39999961853027</v>
       </c>
       <c r="D291">
-        <v>-16.40680694580078</v>
+        <v>-16.96177673339844</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5689,7 +5689,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D292">
-        <v>-3.239547729492188</v>
+        <v>-1.086979150772095</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5703,7 +5703,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D293">
-        <v>0.07196135818958282</v>
+        <v>0.5931349396705627</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5717,7 +5717,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D294">
-        <v>0.2826522886753082</v>
+        <v>-0.1385943442583084</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5731,7 +5731,7 @@
         <v>-4</v>
       </c>
       <c r="D295">
-        <v>-8.333663940429688</v>
+        <v>-9.513779640197754</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5745,7 +5745,7 @@
         <v>-16.60000038146973</v>
       </c>
       <c r="D296">
-        <v>-14.62970638275146</v>
+        <v>-14.75445461273193</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5759,7 +5759,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D297">
-        <v>5.426815986633301</v>
+        <v>4.968177795410156</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5773,7 +5773,7 @@
         <v>-7.199999809265137</v>
       </c>
       <c r="D298">
-        <v>-0.8044692277908325</v>
+        <v>0.5955824255943298</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5787,7 +5787,7 @@
         <v>-20</v>
       </c>
       <c r="D299">
-        <v>-13.77316093444824</v>
+        <v>-14.28847217559814</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5801,7 +5801,7 @@
         <v>-15.30000019073486</v>
       </c>
       <c r="D300">
-        <v>-11.00003814697266</v>
+        <v>-12.10702514648438</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5815,7 +5815,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D301">
-        <v>-3.471821069717407</v>
+        <v>-3.365809440612793</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5829,7 +5829,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D302">
-        <v>-1.231605172157288</v>
+        <v>-2.981701135635376</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5843,7 +5843,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D303">
-        <v>1.421202421188354</v>
+        <v>0.6547567248344421</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5857,7 +5857,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D304">
-        <v>1.062405347824097</v>
+        <v>0.4379741549491882</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5871,7 +5871,7 @@
         <v>22.89999961853027</v>
       </c>
       <c r="D305">
-        <v>10.16252136230469</v>
+        <v>9.710707664489746</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5885,7 +5885,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D306">
-        <v>1.904441833496094</v>
+        <v>2.505406379699707</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5899,7 +5899,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D307">
-        <v>-1.616295576095581</v>
+        <v>-8.167904853820801</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5913,7 +5913,7 @@
         <v>3</v>
       </c>
       <c r="D308">
-        <v>2.619776010513306</v>
+        <v>1.900662302970886</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5927,7 +5927,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D309">
-        <v>-4.47801399230957</v>
+        <v>-1.71261739730835</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5941,7 +5941,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D310">
-        <v>3.25079870223999</v>
+        <v>2.889853954315186</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5955,7 +5955,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D311">
-        <v>2.571270704269409</v>
+        <v>1.843794822692871</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5969,7 +5969,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D312">
-        <v>5.821744918823242</v>
+        <v>2.508524656295776</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5983,7 +5983,7 @@
         <v>-18</v>
       </c>
       <c r="D313">
-        <v>-11.69974708557129</v>
+        <v>-13.1969165802002</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5997,7 +5997,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D314">
-        <v>-7.305100440979004</v>
+        <v>-5.658860683441162</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -6011,7 +6011,7 @@
         <v>-1.5</v>
       </c>
       <c r="D315">
-        <v>1.072713613510132</v>
+        <v>0.5237294435501099</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -6025,7 +6025,7 @@
         <v>-13.10000038146973</v>
       </c>
       <c r="D316">
-        <v>-4.50904655456543</v>
+        <v>-2.260542392730713</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -6039,7 +6039,7 @@
         <v>-33.90000152587891</v>
       </c>
       <c r="D317">
-        <v>-18.68462371826172</v>
+        <v>-22.61173439025879</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -6053,7 +6053,7 @@
         <v>-19.89999961853027</v>
       </c>
       <c r="D318">
-        <v>-12.49317169189453</v>
+        <v>-13.68895244598389</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -6067,7 +6067,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D319">
-        <v>-0.1491276770830154</v>
+        <v>-8.436392784118652</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -6081,7 +6081,7 @@
         <v>-5.300000190734863</v>
       </c>
       <c r="D320">
-        <v>0.5611094832420349</v>
+        <v>1.716607570648193</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -6095,7 +6095,7 @@
         <v>0.5</v>
       </c>
       <c r="D321">
-        <v>-2.200458765029907</v>
+        <v>-0.6577445864677429</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -6109,7 +6109,7 @@
         <v>-9.399999618530273</v>
       </c>
       <c r="D322">
-        <v>-6.063304424285889</v>
+        <v>-3.280178546905518</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -6123,7 +6123,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D323">
-        <v>-2.897051572799683</v>
+        <v>-3.283905267715454</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -6137,7 +6137,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D324">
-        <v>-0.7207866311073303</v>
+        <v>0.1952118128538132</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -6151,7 +6151,7 @@
         <v>8.5</v>
       </c>
       <c r="D325">
-        <v>1.99827253818512</v>
+        <v>2.581399917602539</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -6165,7 +6165,7 @@
         <v>-24.79999923706055</v>
       </c>
       <c r="D326">
-        <v>-15.75109386444092</v>
+        <v>-16.70742034912109</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -6179,7 +6179,7 @@
         <v>11</v>
       </c>
       <c r="D327">
-        <v>4.764188289642334</v>
+        <v>4.452493190765381</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -6193,7 +6193,7 @@
         <v>-6.599999904632568</v>
       </c>
       <c r="D328">
-        <v>-2.3829185962677</v>
+        <v>-1.3941410779953</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -6207,7 +6207,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D329">
-        <v>0.09578266739845276</v>
+        <v>2.045279741287231</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -6221,7 +6221,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D330">
-        <v>6.733571529388428</v>
+        <v>5.431349754333496</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -6235,7 +6235,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D331">
-        <v>-0.2264577001333237</v>
+        <v>0.1875466108322144</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -6249,7 +6249,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D332">
-        <v>2.517689943313599</v>
+        <v>4.103628158569336</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6263,7 +6263,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D333">
-        <v>0.3125538229942322</v>
+        <v>-4.220494270324707</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -6277,7 +6277,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D334">
-        <v>-3.49737286567688</v>
+        <v>-3.747334241867065</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -6291,7 +6291,7 @@
         <v>-30.60000038146973</v>
       </c>
       <c r="D335">
-        <v>-22.88881301879883</v>
+        <v>-19.3557071685791</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -6305,7 +6305,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D336">
-        <v>-5.109402179718018</v>
+        <v>-5.655877113342285</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -6319,7 +6319,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D337">
-        <v>8.370855331420898</v>
+        <v>7.947937965393066</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -6333,7 +6333,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D338">
-        <v>0.6920992732048035</v>
+        <v>-0.333734393119812</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -6347,7 +6347,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D339">
-        <v>-3.810456991195679</v>
+        <v>-4.449922561645508</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -6361,7 +6361,7 @@
         <v>-13.19999980926514</v>
       </c>
       <c r="D340">
-        <v>-12.05523586273193</v>
+        <v>-11.29358768463135</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -6375,7 +6375,7 @@
         <v>-24.20000076293945</v>
       </c>
       <c r="D341">
-        <v>-25.78681373596191</v>
+        <v>-28.75336265563965</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6389,7 +6389,7 @@
         <v>-12.5</v>
       </c>
       <c r="D342">
-        <v>-7.818333625793457</v>
+        <v>-10.37670803070068</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6403,7 +6403,7 @@
         <v>-34.5</v>
       </c>
       <c r="D343">
-        <v>-17.68852615356445</v>
+        <v>-17.85833168029785</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6417,7 +6417,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D344">
-        <v>2.290419816970825</v>
+        <v>0.9266670942306519</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6431,7 +6431,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D345">
-        <v>2.873554468154907</v>
+        <v>3.336501836776733</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6445,7 +6445,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D346">
-        <v>3.014411687850952</v>
+        <v>4.054134845733643</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6459,7 +6459,7 @@
         <v>2.5</v>
       </c>
       <c r="D347">
-        <v>3.366503477096558</v>
+        <v>2.797847747802734</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6473,7 +6473,7 @@
         <v>-22.60000038146973</v>
       </c>
       <c r="D348">
-        <v>-13.16567993164062</v>
+        <v>-14.38559341430664</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6487,7 +6487,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D349">
-        <v>-0.2955743074417114</v>
+        <v>0.4887940883636475</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6501,7 +6501,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D350">
-        <v>-1.072728872299194</v>
+        <v>-0.8982388973236084</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6515,7 +6515,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D351">
-        <v>1.840058922767639</v>
+        <v>1.998283386230469</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6529,7 +6529,7 @@
         <v>-8.800000190734863</v>
       </c>
       <c r="D352">
-        <v>-6.933834075927734</v>
+        <v>-2.800825595855713</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6543,7 +6543,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D353">
-        <v>2.122610092163086</v>
+        <v>0.6925379037857056</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6557,7 +6557,7 @@
         <v>-18.5</v>
       </c>
       <c r="D354">
-        <v>-12.76657581329346</v>
+        <v>-13.80553150177002</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6571,7 +6571,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D355">
-        <v>-2.903187036514282</v>
+        <v>-0.4115900993347168</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6585,7 +6585,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D356">
-        <v>2.56233024597168</v>
+        <v>1.367803454399109</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6599,7 +6599,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D357">
-        <v>2.978649854660034</v>
+        <v>1.35534393787384</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6613,7 +6613,7 @@
         <v>-15.10000038146973</v>
       </c>
       <c r="D358">
-        <v>-10.90633201599121</v>
+        <v>-9.598867416381836</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6627,7 +6627,7 @@
         <v>-19.5</v>
       </c>
       <c r="D359">
-        <v>-11.02093982696533</v>
+        <v>-12.31303119659424</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6641,7 +6641,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D360">
-        <v>1.647734642028809</v>
+        <v>2.023632287979126</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6655,7 +6655,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D361">
-        <v>1.458789825439453</v>
+        <v>1.143313527107239</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6669,7 +6669,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D362">
-        <v>3.832704544067383</v>
+        <v>3.34888219833374</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6683,7 +6683,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D363">
-        <v>-5.457651138305664</v>
+        <v>-6.841708183288574</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6697,7 +6697,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D364">
-        <v>1.579694032669067</v>
+        <v>4.614083766937256</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6711,7 +6711,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D365">
-        <v>-4.930401802062988</v>
+        <v>-5.555294036865234</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6725,7 +6725,7 @@
         <v>18.79999923706055</v>
       </c>
       <c r="D366">
-        <v>6.080211639404297</v>
+        <v>8.616463661193848</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6739,7 +6739,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D367">
-        <v>1.257671117782593</v>
+        <v>0.009277120232582092</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6753,7 +6753,7 @@
         <v>-5.300000190734863</v>
       </c>
       <c r="D368">
-        <v>-3.967917680740356</v>
+        <v>-4.139807224273682</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6767,7 +6767,7 @@
         <v>-10.89999961853027</v>
       </c>
       <c r="D369">
-        <v>-10.90786933898926</v>
+        <v>-7.404372215270996</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6781,7 +6781,7 @@
         <v>-30.79999923706055</v>
       </c>
       <c r="D370">
-        <v>-18.69298553466797</v>
+        <v>-21.7110710144043</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6795,7 +6795,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D371">
-        <v>5.280428886413574</v>
+        <v>1.630032300949097</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6809,7 +6809,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D372">
-        <v>-1.128114461898804</v>
+        <v>-0.1065924167633057</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6823,7 +6823,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D373">
-        <v>-2.28026270866394</v>
+        <v>-3.047438383102417</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6837,7 +6837,7 @@
         <v>4.5</v>
       </c>
       <c r="D374">
-        <v>5.299622058868408</v>
+        <v>3.40251898765564</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6851,7 +6851,7 @@
         <v>-2.5</v>
       </c>
       <c r="D375">
-        <v>-6.602204322814941</v>
+        <v>-10.8958158493042</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6865,7 +6865,7 @@
         <v>-31</v>
       </c>
       <c r="D376">
-        <v>-16.57785224914551</v>
+        <v>-14.97262668609619</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6879,7 +6879,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D377">
-        <v>1.542408466339111</v>
+        <v>0.4575952887535095</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="D378">
-        <v>1.366910934448242</v>
+        <v>0.4578523635864258</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6907,7 +6907,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D379">
-        <v>2.731645345687866</v>
+        <v>4.035751342773438</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6921,7 +6921,7 @@
         <v>5</v>
       </c>
       <c r="D380">
-        <v>3.329911708831787</v>
+        <v>4.215383052825928</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6935,7 +6935,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D381">
-        <v>-0.9206007719039917</v>
+        <v>0.1581828594207764</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6949,7 +6949,7 @@
         <v>-10.10000038146973</v>
       </c>
       <c r="D382">
-        <v>-4.265564441680908</v>
+        <v>-6.584908008575439</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6963,7 +6963,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D383">
-        <v>6.169660568237305</v>
+        <v>5.661539554595947</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6977,7 +6977,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D384">
-        <v>11.7017822265625</v>
+        <v>11.15468883514404</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -6991,7 +6991,7 @@
         <v>-30.89999961853027</v>
       </c>
       <c r="D385">
-        <v>-20.06147575378418</v>
+        <v>-17.17639541625977</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -7005,7 +7005,7 @@
         <v>-3</v>
       </c>
       <c r="D386">
-        <v>1.283815622329712</v>
+        <v>1.34265673160553</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -7019,7 +7019,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D387">
-        <v>3.22680139541626</v>
+        <v>2.263638734817505</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -7033,7 +7033,7 @@
         <v>-6</v>
       </c>
       <c r="D388">
-        <v>-1.582691669464111</v>
+        <v>-2.944840669631958</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -7047,7 +7047,7 @@
         <v>-8.699999809265137</v>
       </c>
       <c r="D389">
-        <v>-1.393783926963806</v>
+        <v>0.11949223279953</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -7061,7 +7061,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D390">
-        <v>2.887709379196167</v>
+        <v>2.489743947982788</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -7075,7 +7075,7 @@
         <v>3</v>
       </c>
       <c r="D391">
-        <v>6.56891918182373</v>
+        <v>5.729416370391846</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -7089,7 +7089,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D392">
-        <v>-2.614102602005005</v>
+        <v>0.1082535535097122</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -7103,7 +7103,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D393">
-        <v>-0.3035441637039185</v>
+        <v>0.6345905065536499</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -7117,7 +7117,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D394">
-        <v>1.27603805065155</v>
+        <v>0.3550571203231812</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -7131,7 +7131,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D395">
-        <v>-2.659614324569702</v>
+        <v>-2.776314973831177</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -7145,7 +7145,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D396">
-        <v>2.804725885391235</v>
+        <v>1.710513114929199</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -7159,7 +7159,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D397">
-        <v>3.431821823120117</v>
+        <v>-1.02512788772583</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -7173,7 +7173,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D398">
-        <v>-3.069944620132446</v>
+        <v>-2.416827440261841</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -7187,7 +7187,7 @@
         <v>-16.20000076293945</v>
       </c>
       <c r="D399">
-        <v>-12.07290077209473</v>
+        <v>-11.18626117706299</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -7201,7 +7201,7 @@
         <v>8</v>
       </c>
       <c r="D400">
-        <v>3.385624408721924</v>
+        <v>2.099815368652344</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7215,7 +7215,7 @@
         <v>-11</v>
       </c>
       <c r="D401">
-        <v>-4.265268325805664</v>
+        <v>-4.401241779327393</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -7229,7 +7229,7 @@
         <v>13.60000038146973</v>
       </c>
       <c r="D402">
-        <v>5.512538433074951</v>
+        <v>4.677721500396729</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -7243,7 +7243,7 @@
         <v>-22.79999923706055</v>
       </c>
       <c r="D403">
-        <v>-17.37654304504395</v>
+        <v>-19.14819145202637</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7257,7 +7257,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D404">
-        <v>-0.5806006193161011</v>
+        <v>0.9356582164764404</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -7271,7 +7271,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D405">
-        <v>3.412481069564819</v>
+        <v>3.500051259994507</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7285,7 +7285,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D406">
-        <v>-5.955209732055664</v>
+        <v>-6.463559627532959</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7299,7 +7299,7 @@
         <v>-10.89999961853027</v>
       </c>
       <c r="D407">
-        <v>-7.955625534057617</v>
+        <v>-8.332337379455566</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7313,7 +7313,7 @@
         <v>2</v>
       </c>
       <c r="D408">
-        <v>2.300462245941162</v>
+        <v>2.652300357818604</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7327,7 +7327,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D409">
-        <v>2.040226459503174</v>
+        <v>0.9473310708999634</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -7341,7 +7341,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D410">
-        <v>1.167445540428162</v>
+        <v>0.3361838459968567</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -7355,7 +7355,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D411">
-        <v>2.732868194580078</v>
+        <v>1.885436058044434</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -7369,7 +7369,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D412">
-        <v>2.161652088165283</v>
+        <v>1.578324794769287</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -7383,7 +7383,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D413">
-        <v>-4.888359069824219</v>
+        <v>-4.127933025360107</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7397,7 +7397,7 @@
         <v>-14.60000038146973</v>
       </c>
       <c r="D414">
-        <v>-11.88242530822754</v>
+        <v>-12.30384635925293</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7411,7 +7411,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D415">
-        <v>-2.25441575050354</v>
+        <v>-1.070146083831787</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7425,7 +7425,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D416">
-        <v>2.393212556838989</v>
+        <v>1.662553548812866</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7439,7 +7439,7 @@
         <v>-9</v>
       </c>
       <c r="D417">
-        <v>-1.344787955284119</v>
+        <v>-2.54737401008606</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7453,7 +7453,7 @@
         <v>-32.20000076293945</v>
       </c>
       <c r="D418">
-        <v>-32.66539001464844</v>
+        <v>-32.76388168334961</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7467,7 +7467,7 @@
         <v>-21.29999923706055</v>
       </c>
       <c r="D419">
-        <v>-13.7924165725708</v>
+        <v>-12.69288349151611</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7481,7 +7481,7 @@
         <v>2</v>
       </c>
       <c r="D420">
-        <v>2.216451406478882</v>
+        <v>2.250214338302612</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7495,7 +7495,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D421">
-        <v>3.667708158493042</v>
+        <v>4.710411548614502</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7509,7 +7509,7 @@
         <v>18.20000076293945</v>
       </c>
       <c r="D422">
-        <v>9.46640682220459</v>
+        <v>10.39546966552734</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7523,7 +7523,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D423">
-        <v>-0.0422077476978302</v>
+        <v>-0.5595204830169678</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7537,7 +7537,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D424">
-        <v>-2.552200078964233</v>
+        <v>-2.513925313949585</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7551,7 +7551,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D425">
-        <v>2.650768518447876</v>
+        <v>2.170604705810547</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7565,7 +7565,7 @@
         <v>-30.29999923706055</v>
       </c>
       <c r="D426">
-        <v>-11.58726692199707</v>
+        <v>-18.47044944763184</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7579,7 +7579,7 @@
         <v>-16</v>
       </c>
       <c r="D427">
-        <v>-10.65096950531006</v>
+        <v>-5.905803680419922</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7593,7 +7593,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D428">
-        <v>0.2439193874597549</v>
+        <v>0.2713943123817444</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7607,7 +7607,7 @@
         <v>-14.30000019073486</v>
       </c>
       <c r="D429">
-        <v>-6.671486377716064</v>
+        <v>-4.715744495391846</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7621,7 +7621,7 @@
         <v>-11.5</v>
       </c>
       <c r="D430">
-        <v>-8.91682243347168</v>
+        <v>-4.866724491119385</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7635,7 +7635,7 @@
         <v>-2.5</v>
       </c>
       <c r="D431">
-        <v>-1.084391117095947</v>
+        <v>-2.563518047332764</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7649,7 +7649,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D432">
-        <v>-0.280445396900177</v>
+        <v>-1.458842635154724</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7663,7 +7663,7 @@
         <v>-4</v>
       </c>
       <c r="D433">
-        <v>0.1224928200244904</v>
+        <v>4.056461811065674</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7677,7 +7677,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D434">
-        <v>-0.4460451006889343</v>
+        <v>1.686222553253174</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7691,7 +7691,7 @@
         <v>1</v>
       </c>
       <c r="D435">
-        <v>1.677926540374756</v>
+        <v>0.4501456022262573</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7705,7 +7705,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D436">
-        <v>2.71701455116272</v>
+        <v>1.218088388442993</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7719,7 +7719,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D437">
-        <v>2.049923658370972</v>
+        <v>1.355543255805969</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7733,7 +7733,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D438">
-        <v>1.990089416503906</v>
+        <v>0.3460186719894409</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7747,7 +7747,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D439">
-        <v>3.397671937942505</v>
+        <v>4.103556632995605</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7761,7 +7761,7 @@
         <v>-2</v>
       </c>
       <c r="D440">
-        <v>1.818350076675415</v>
+        <v>0.8490785360336304</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7775,7 +7775,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D441">
-        <v>3.403356313705444</v>
+        <v>3.625576257705688</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7789,7 +7789,7 @@
         <v>-1</v>
       </c>
       <c r="D442">
-        <v>1.163841605186462</v>
+        <v>-1.261639595031738</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7803,7 +7803,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D443">
-        <v>-2.89145302772522</v>
+        <v>-5.334737300872803</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7817,7 +7817,7 @@
         <v>20.70000076293945</v>
       </c>
       <c r="D444">
-        <v>16.28224945068359</v>
+        <v>16.24535942077637</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7831,7 +7831,7 @@
         <v>16.10000038146973</v>
       </c>
       <c r="D445">
-        <v>6.315838813781738</v>
+        <v>8.401982307434082</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7845,7 +7845,7 @@
         <v>4</v>
       </c>
       <c r="D446">
-        <v>-0.794889509677887</v>
+        <v>0.7606606483459473</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7859,7 +7859,7 @@
         <v>34.79999923706055</v>
       </c>
       <c r="D447">
-        <v>18.50732803344727</v>
+        <v>16.83529472351074</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7873,7 +7873,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D448">
-        <v>2.286216974258423</v>
+        <v>2.134626388549805</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -7887,7 +7887,7 @@
         <v>10.30000019073486</v>
       </c>
       <c r="D449">
-        <v>5.888942718505859</v>
+        <v>6.418005466461182</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -7901,7 +7901,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D450">
-        <v>-0.4161045551300049</v>
+        <v>0.1796849966049194</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -7915,7 +7915,7 @@
         <v>-16.10000038146973</v>
       </c>
       <c r="D451">
-        <v>-11.75646781921387</v>
+        <v>-15.54128456115723</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -7929,7 +7929,7 @@
         <v>-4</v>
       </c>
       <c r="D452">
-        <v>-1.19965660572052</v>
+        <v>-1.992587804794312</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -7943,7 +7943,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D453">
-        <v>-4.01025390625</v>
+        <v>-4.957283973693848</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -7957,7 +7957,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D454">
-        <v>0.6925147771835327</v>
+        <v>0.6461343765258789</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -7971,7 +7971,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D455">
-        <v>-4.224688529968262</v>
+        <v>-4.104518890380859</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -7985,7 +7985,7 @@
         <v>33.5</v>
       </c>
       <c r="D456">
-        <v>24.55542755126953</v>
+        <v>23.12075805664062</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -7999,7 +7999,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D457">
-        <v>2.085978746414185</v>
+        <v>2.567063331604004</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -8013,7 +8013,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D458">
-        <v>-0.7734702825546265</v>
+        <v>-3.447019338607788</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -8027,7 +8027,7 @@
         <v>-5.300000190734863</v>
       </c>
       <c r="D459">
-        <v>-4.463990211486816</v>
+        <v>-4.318942546844482</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -8041,7 +8041,7 @@
         <v>-5</v>
       </c>
       <c r="D460">
-        <v>1.52852725982666</v>
+        <v>0.7196886539459229</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -8055,7 +8055,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D461">
-        <v>-0.1580448895692825</v>
+        <v>0.1153068020939827</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -8069,7 +8069,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D462">
-        <v>-3.386552095413208</v>
+        <v>-1.698645353317261</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -8083,7 +8083,7 @@
         <v>-2</v>
       </c>
       <c r="D463">
-        <v>-1.394904851913452</v>
+        <v>-1.021387338638306</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -8097,7 +8097,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D464">
-        <v>1.18415367603302</v>
+        <v>1.331296324729919</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -8111,7 +8111,7 @@
         <v>-11.89999961853027</v>
       </c>
       <c r="D465">
-        <v>-11.67094039916992</v>
+        <v>-10.2126932144165</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -8125,7 +8125,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D466">
-        <v>-0.1347260028123856</v>
+        <v>0.3284035921096802</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -8139,7 +8139,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D467">
-        <v>2.96229362487793</v>
+        <v>2.397683382034302</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -8153,7 +8153,7 @@
         <v>-6.5</v>
       </c>
       <c r="D468">
-        <v>-5.346538543701172</v>
+        <v>-4.488260746002197</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -8167,7 +8167,7 @@
         <v>14</v>
       </c>
       <c r="D469">
-        <v>5.15663480758667</v>
+        <v>4.259801864624023</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -8181,7 +8181,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D470">
-        <v>-0.240301176905632</v>
+        <v>1.455881834030151</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -8195,7 +8195,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D471">
-        <v>0.2587440609931946</v>
+        <v>0.07728929072618484</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -8209,7 +8209,7 @@
         <v>-10.80000019073486</v>
       </c>
       <c r="D472">
-        <v>-5.566132545471191</v>
+        <v>-5.897480487823486</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -8223,7 +8223,7 @@
         <v>-0.5</v>
       </c>
       <c r="D473">
-        <v>3.359391689300537</v>
+        <v>3.27333664894104</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -8237,7 +8237,7 @@
         <v>5.5</v>
       </c>
       <c r="D474">
-        <v>6.207082748413086</v>
+        <v>5.363890171051025</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -8251,7 +8251,7 @@
         <v>22.60000038146973</v>
       </c>
       <c r="D475">
-        <v>11.29290008544922</v>
+        <v>10.89915180206299</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -8265,7 +8265,7 @@
         <v>-8.199999809265137</v>
       </c>
       <c r="D476">
-        <v>-6.996524333953857</v>
+        <v>-6.502856731414795</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -8279,7 +8279,7 @@
         <v>-8.5</v>
       </c>
       <c r="D477">
-        <v>-9.162036895751953</v>
+        <v>-4.315871238708496</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -8293,7 +8293,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D478">
-        <v>0.9910913705825806</v>
+        <v>0.8368213176727295</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -8307,7 +8307,7 @@
         <v>-9.600000381469727</v>
       </c>
       <c r="D479">
-        <v>-6.477719783782959</v>
+        <v>-10.77719402313232</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -8321,7 +8321,7 @@
         <v>-5</v>
       </c>
       <c r="D480">
-        <v>2.018620729446411</v>
+        <v>0.1915552169084549</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -8335,7 +8335,7 @@
         <v>1.5</v>
       </c>
       <c r="D481">
-        <v>1.789127588272095</v>
+        <v>-0.1501535624265671</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -8349,7 +8349,7 @@
         <v>-6.5</v>
       </c>
       <c r="D482">
-        <v>-5.948732376098633</v>
+        <v>-4.154774188995361</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -8363,7 +8363,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D483">
-        <v>1.500150918960571</v>
+        <v>0.5587348937988281</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -8377,7 +8377,7 @@
         <v>0.5</v>
       </c>
       <c r="D484">
-        <v>2.991425752639771</v>
+        <v>2.535080194473267</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8391,7 +8391,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D485">
-        <v>1.899388909339905</v>
+        <v>3.648568630218506</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -8405,7 +8405,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D486">
-        <v>1.184993267059326</v>
+        <v>0.1006988137960434</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -8419,7 +8419,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D487">
-        <v>-9.031185150146484</v>
+        <v>-9.910102844238281</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8433,7 +8433,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D488">
-        <v>7.968729496002197</v>
+        <v>8.250739097595215</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8447,7 +8447,7 @@
         <v>7</v>
       </c>
       <c r="D489">
-        <v>2.764426946640015</v>
+        <v>2.087885618209839</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8461,7 +8461,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D490">
-        <v>-6.14321231842041</v>
+        <v>-6.230251312255859</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8475,7 +8475,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D491">
-        <v>-7.177732944488525</v>
+        <v>-7.644320011138916</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -8489,7 +8489,7 @@
         <v>5.5</v>
       </c>
       <c r="D492">
-        <v>2.112454414367676</v>
+        <v>2.430867195129395</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8503,7 +8503,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D493">
-        <v>1.827582836151123</v>
+        <v>0.494744598865509</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -8517,7 +8517,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D494">
-        <v>-0.02205872535705566</v>
+        <v>-0.09599557518959045</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8531,7 +8531,7 @@
         <v>-1</v>
       </c>
       <c r="D495">
-        <v>-1.808049559593201</v>
+        <v>-1.140191316604614</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -8545,7 +8545,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D496">
-        <v>0.4265177845954895</v>
+        <v>0.03530707955360413</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8559,7 +8559,7 @@
         <v>-14.30000019073486</v>
       </c>
       <c r="D497">
-        <v>-6.539472103118896</v>
+        <v>-9.055371284484863</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8573,7 +8573,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D498">
-        <v>-5.273709297180176</v>
+        <v>-4.531849384307861</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8587,7 +8587,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D499">
-        <v>3.437089681625366</v>
+        <v>3.062616348266602</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8601,7 +8601,7 @@
         <v>-3.5</v>
       </c>
       <c r="D500">
-        <v>-1.605631351470947</v>
+        <v>-4.298824787139893</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8615,7 +8615,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D501">
-        <v>7.372691631317139</v>
+        <v>5.984672069549561</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8629,7 +8629,7 @@
         <v>10.5</v>
       </c>
       <c r="D502">
-        <v>5.580782413482666</v>
+        <v>6.663883686065674</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -8643,7 +8643,7 @@
         <v>-7.900000095367432</v>
       </c>
       <c r="D503">
-        <v>-1.894497156143188</v>
+        <v>-2.924197435379028</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -8657,7 +8657,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D504">
-        <v>2.423214197158813</v>
+        <v>2.744282007217407</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -8671,7 +8671,7 @@
         <v>-10.60000038146973</v>
       </c>
       <c r="D505">
-        <v>-1.534086108207703</v>
+        <v>-6.539763927459717</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -8685,7 +8685,7 @@
         <v>22</v>
       </c>
       <c r="D506">
-        <v>14.07292556762695</v>
+        <v>17.05665016174316</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -8699,7 +8699,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D507">
-        <v>-2.93950629234314</v>
+        <v>-3.486880779266357</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -8713,7 +8713,7 @@
         <v>-4.5</v>
       </c>
       <c r="D508">
-        <v>1.76771879196167</v>
+        <v>0.8412868976593018</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -8727,7 +8727,7 @@
         <v>-5.5</v>
       </c>
       <c r="D509">
-        <v>2.716870784759521</v>
+        <v>2.856491327285767</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -8741,7 +8741,7 @@
         <v>-6.5</v>
       </c>
       <c r="D510">
-        <v>-11.0134449005127</v>
+        <v>-12.23349857330322</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -8755,7 +8755,7 @@
         <v>1</v>
       </c>
       <c r="D511">
-        <v>2.029502868652344</v>
+        <v>0.9204274415969849</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -8769,7 +8769,7 @@
         <v>14.39999961853027</v>
       </c>
       <c r="D512">
-        <v>10.27148628234863</v>
+        <v>11.13449954986572</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -8783,7 +8783,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D513">
-        <v>-0.4217429161071777</v>
+        <v>1.200193166732788</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -8797,7 +8797,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D514">
-        <v>1.9012850522995</v>
+        <v>3.441098690032959</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -8811,7 +8811,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D515">
-        <v>1.461099147796631</v>
+        <v>-0.1534972935914993</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -8825,7 +8825,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D516">
-        <v>4.641086578369141</v>
+        <v>3.397880554199219</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -8839,7 +8839,7 @@
         <v>-25.60000038146973</v>
       </c>
       <c r="D517">
-        <v>-11.55355262756348</v>
+        <v>-12.71449565887451</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -8853,7 +8853,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D518">
-        <v>6.742333889007568</v>
+        <v>8.37495231628418</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -8867,7 +8867,7 @@
         <v>3.5</v>
       </c>
       <c r="D519">
-        <v>1.500603914260864</v>
+        <v>0.9298337697982788</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -8881,7 +8881,7 @@
         <v>4.5</v>
       </c>
       <c r="D520">
-        <v>6.675117969512939</v>
+        <v>7.037861347198486</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -8895,7 +8895,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D521">
-        <v>0.8292125463485718</v>
+        <v>1.201638579368591</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -8909,7 +8909,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D522">
-        <v>2.209175109863281</v>
+        <v>2.459400653839111</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -8923,7 +8923,7 @@
         <v>13.39999961853027</v>
       </c>
       <c r="D523">
-        <v>8.62697696685791</v>
+        <v>7.775187969207764</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -8937,7 +8937,7 @@
         <v>24.79999923706055</v>
       </c>
       <c r="D524">
-        <v>7.741858005523682</v>
+        <v>11.78199768066406</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -8951,7 +8951,7 @@
         <v>-11.80000019073486</v>
       </c>
       <c r="D525">
-        <v>-6.152598857879639</v>
+        <v>-12.55495738983154</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -8965,7 +8965,7 @@
         <v>-16.79999923706055</v>
       </c>
       <c r="D526">
-        <v>-13.0845890045166</v>
+        <v>-14.15791034698486</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -8979,7 +8979,7 @@
         <v>4</v>
       </c>
       <c r="D527">
-        <v>1.071272850036621</v>
+        <v>2.032724380493164</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -8993,7 +8993,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D528">
-        <v>-3.385508298873901</v>
+        <v>-3.974016904830933</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -9007,7 +9007,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D529">
-        <v>2.295487642288208</v>
+        <v>1.604029178619385</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -9021,7 +9021,7 @@
         <v>-33.29999923706055</v>
       </c>
       <c r="D530">
-        <v>-18.38744735717773</v>
+        <v>-20.78849601745605</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9035,7 +9035,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D531">
-        <v>4.441854476928711</v>
+        <v>4.627024173736572</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -9049,7 +9049,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D532">
-        <v>0.9906362891197205</v>
+        <v>2.335310697555542</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -9063,7 +9063,7 @@
         <v>-15.30000019073486</v>
       </c>
       <c r="D533">
-        <v>-12.67412853240967</v>
+        <v>-12.65028095245361</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -9077,7 +9077,7 @@
         <v>23.10000038146973</v>
       </c>
       <c r="D534">
-        <v>15.94174480438232</v>
+        <v>16.92483901977539</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9091,7 +9091,7 @@
         <v>-13.89999961853027</v>
       </c>
       <c r="D535">
-        <v>-8.869845390319824</v>
+        <v>-8.189967155456543</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -9105,7 +9105,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D536">
-        <v>0.04554365575313568</v>
+        <v>0.518534243106842</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -9119,7 +9119,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D537">
-        <v>-1.771047353744507</v>
+        <v>-1.556212067604065</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -9133,7 +9133,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D538">
-        <v>2.077601671218872</v>
+        <v>3.797199964523315</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -9147,7 +9147,7 @@
         <v>-11.5</v>
       </c>
       <c r="D539">
-        <v>-9.556020736694336</v>
+        <v>-9.713784217834473</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -9161,7 +9161,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D540">
-        <v>3.830579996109009</v>
+        <v>3.704946994781494</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9175,7 +9175,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D541">
-        <v>2.537842988967896</v>
+        <v>2.128117084503174</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -9189,7 +9189,7 @@
         <v>-55.20000076293945</v>
       </c>
       <c r="D542">
-        <v>-37.07994842529297</v>
+        <v>-38.13617706298828</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -9203,7 +9203,7 @@
         <v>-16.20000076293945</v>
       </c>
       <c r="D543">
-        <v>-7.842187881469727</v>
+        <v>-9.067275047302246</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9217,7 +9217,7 @@
         <v>8</v>
       </c>
       <c r="D544">
-        <v>3.931960105895996</v>
+        <v>2.925981760025024</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9231,7 +9231,7 @@
         <v>-11.80000019073486</v>
       </c>
       <c r="D545">
-        <v>-7.347188472747803</v>
+        <v>-7.555760860443115</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -9245,7 +9245,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D546">
-        <v>2.273346662521362</v>
+        <v>3.266137599945068</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9259,7 +9259,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D547">
-        <v>-2.268137693405151</v>
+        <v>-2.60868763923645</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9273,7 +9273,7 @@
         <v>16.39999961853027</v>
       </c>
       <c r="D548">
-        <v>6.437916278839111</v>
+        <v>5.352633953094482</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -9287,7 +9287,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D549">
-        <v>-1.09421169757843</v>
+        <v>0.8460187911987305</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9301,7 +9301,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D550">
-        <v>-7.225060939788818</v>
+        <v>-4.859681606292725</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9315,7 +9315,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D551">
-        <v>-2.345926284790039</v>
+        <v>-2.290321826934814</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -9329,7 +9329,7 @@
         <v>7</v>
       </c>
       <c r="D552">
-        <v>3.775136470794678</v>
+        <v>5.921774864196777</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9343,7 +9343,7 @@
         <v>1</v>
       </c>
       <c r="D553">
-        <v>0.6462007164955139</v>
+        <v>1.20297646522522</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -9357,7 +9357,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D554">
-        <v>0.7988947629928589</v>
+        <v>1.343477606773376</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -9371,7 +9371,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D555">
-        <v>3.200573921203613</v>
+        <v>4.892026901245117</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -9385,7 +9385,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D556">
-        <v>0.8112068176269531</v>
+        <v>0.3287270963191986</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -9399,7 +9399,7 @@
         <v>5.5</v>
       </c>
       <c r="D557">
-        <v>0.9035069942474365</v>
+        <v>2.497855424880981</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -9413,7 +9413,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D558">
-        <v>4.101821899414062</v>
+        <v>3.554970502853394</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -9427,7 +9427,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D559">
-        <v>1.493632912635803</v>
+        <v>-0.02382795512676239</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -9441,7 +9441,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D560">
-        <v>4.071484088897705</v>
+        <v>4.738610744476318</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -9455,7 +9455,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D561">
-        <v>0.9430975317955017</v>
+        <v>0.7348358631134033</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -9469,7 +9469,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D562">
-        <v>2.237641572952271</v>
+        <v>2.798513174057007</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -9483,7 +9483,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D563">
-        <v>-0.3824539184570312</v>
+        <v>0.1910048723220825</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -9497,7 +9497,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D564">
-        <v>5.630200386047363</v>
+        <v>6.697764873504639</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -9511,7 +9511,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D565">
-        <v>1.701242685317993</v>
+        <v>7.299886226654053</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -9525,7 +9525,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D566">
-        <v>4.309805870056152</v>
+        <v>3.677448987960815</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -9539,7 +9539,7 @@
         <v>10.60000038146973</v>
       </c>
       <c r="D567">
-        <v>11.93812561035156</v>
+        <v>11.03314876556396</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -9553,7 +9553,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D568">
-        <v>-2.004885196685791</v>
+        <v>-3.3131103515625</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -9567,7 +9567,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D569">
-        <v>1.692155122756958</v>
+        <v>0.4995371103286743</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -9581,7 +9581,7 @@
         <v>16.20000076293945</v>
       </c>
       <c r="D570">
-        <v>14.67348384857178</v>
+        <v>12.14662647247314</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -9595,7 +9595,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D571">
-        <v>1.527111530303955</v>
+        <v>0.05691181123256683</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -9609,7 +9609,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D572">
-        <v>-0.9323242902755737</v>
+        <v>-1.867871880531311</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -9623,7 +9623,7 @@
         <v>1</v>
       </c>
       <c r="D573">
-        <v>1.637866973876953</v>
+        <v>0.759458065032959</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -9637,7 +9637,7 @@
         <v>-1.5</v>
       </c>
       <c r="D574">
-        <v>1.303304433822632</v>
+        <v>0.7237701416015625</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -9651,7 +9651,7 @@
         <v>3.5</v>
       </c>
       <c r="D575">
-        <v>4.132480621337891</v>
+        <v>2.396779298782349</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -9665,7 +9665,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D576">
-        <v>-1.183871507644653</v>
+        <v>-0.2447790652513504</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -9679,7 +9679,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D577">
-        <v>-7.138119220733643</v>
+        <v>-4.759784698486328</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -9693,7 +9693,7 @@
         <v>-9.100000381469727</v>
       </c>
       <c r="D578">
-        <v>-6.973949432373047</v>
+        <v>-7.055299282073975</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -9707,7 +9707,7 @@
         <v>-23.39999961853027</v>
       </c>
       <c r="D579">
-        <v>-13.99558353424072</v>
+        <v>-13.56069469451904</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -9721,7 +9721,7 @@
         <v>-10</v>
       </c>
       <c r="D580">
-        <v>-5.09808874130249</v>
+        <v>-5.485828399658203</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -9735,7 +9735,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D581">
-        <v>-3.516824007034302</v>
+        <v>-4.032978534698486</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -9749,7 +9749,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D582">
-        <v>2.322848796844482</v>
+        <v>0.9434393644332886</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -9763,7 +9763,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D583">
-        <v>-20.8626594543457</v>
+        <v>-18.54363059997559</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -9777,7 +9777,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D584">
-        <v>2.88700270652771</v>
+        <v>4.075009346008301</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -9791,7 +9791,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D585">
-        <v>7.115106105804443</v>
+        <v>8.395995140075684</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -9805,7 +9805,7 @@
         <v>15.19999980926514</v>
       </c>
       <c r="D586">
-        <v>10.60469818115234</v>
+        <v>8.560675621032715</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -9819,7 +9819,7 @@
         <v>0</v>
       </c>
       <c r="D587">
-        <v>-0.325166642665863</v>
+        <v>-1.703978300094604</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -9833,7 +9833,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D588">
-        <v>3.229455709457397</v>
+        <v>3.015883684158325</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -9847,7 +9847,7 @@
         <v>-11.89999961853027</v>
       </c>
       <c r="D589">
-        <v>-8.700884819030762</v>
+        <v>-8.806544303894043</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -9861,7 +9861,7 @@
         <v>-1</v>
       </c>
       <c r="D590">
-        <v>-1.282926797866821</v>
+        <v>-2.106911182403564</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -9875,7 +9875,7 @@
         <v>-8.399999618530273</v>
       </c>
       <c r="D591">
-        <v>0.739111065864563</v>
+        <v>0.05570252984762192</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -9889,7 +9889,7 @@
         <v>-21.10000038146973</v>
       </c>
       <c r="D592">
-        <v>-27.000244140625</v>
+        <v>-24.65863227844238</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -9903,7 +9903,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D593">
-        <v>2.214728593826294</v>
+        <v>2.539273977279663</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -9917,7 +9917,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D594">
-        <v>3.86898136138916</v>
+        <v>3.490675210952759</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -9931,7 +9931,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D595">
-        <v>1.257996320724487</v>
+        <v>0.7762846946716309</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -9945,7 +9945,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D596">
-        <v>1.642965793609619</v>
+        <v>-0.5797778367996216</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -9959,7 +9959,7 @@
         <v>-11.10000038146973</v>
       </c>
       <c r="D597">
-        <v>-8.867341041564941</v>
+        <v>-8.664520263671875</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -9973,7 +9973,7 @@
         <v>-2</v>
       </c>
       <c r="D598">
-        <v>-1.014235496520996</v>
+        <v>0.6746091842651367</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -9987,7 +9987,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D599">
-        <v>1.491981744766235</v>
+        <v>0.7909845113754272</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -10001,7 +10001,7 @@
         <v>-9.699999809265137</v>
       </c>
       <c r="D600">
-        <v>-6.248673915863037</v>
+        <v>-4.394888401031494</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -10015,7 +10015,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D601">
-        <v>1.575270295143127</v>
+        <v>0.7941367030143738</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -10029,7 +10029,7 @@
         <v>-18.39999961853027</v>
       </c>
       <c r="D602">
-        <v>-14.84298992156982</v>
+        <v>-14.21604824066162</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -10043,7 +10043,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D603">
-        <v>3.493583679199219</v>
+        <v>2.553871870040894</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -10057,7 +10057,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D604">
-        <v>-0.8103839755058289</v>
+        <v>0.3127000331878662</v>
       </c>
     </row>
   </sheetData>
